--- a/Крутагидон_база_карт.xlsx
+++ b/Крутагидон_база_карт.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Gor\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Gor\Downloads\Telegram Desktop\krutagidon\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{40204098-FEFC-4DDF-ABD9-237669D8247D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{99A01943-401C-472F-A622-97FFD579BAD1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-105" yWindow="0" windowWidth="14610" windowHeight="15585" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-105" yWindow="0" windowWidth="14610" windowHeight="15585" firstSheet="1" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Инструкция" sheetId="1" r:id="rId1"/>
@@ -2358,7 +2358,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="40">
+  <cellXfs count="42">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -2406,14 +2406,20 @@
     <xf numFmtId="0" fontId="6" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -2436,15 +2442,13 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
@@ -2936,7 +2940,7 @@
       </c>
     </row>
     <row r="2" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A2" s="37" t="s">
+      <c r="A2" s="27" t="s">
         <v>252</v>
       </c>
       <c r="B2" s="7" t="s">
@@ -2984,7 +2988,7 @@
       <c r="T2" s="5"/>
     </row>
     <row r="3" spans="1:20" ht="26.25" x14ac:dyDescent="0.25">
-      <c r="A3" s="37" t="s">
+      <c r="A3" s="27" t="s">
         <v>253</v>
       </c>
       <c r="B3" s="7" t="s">
@@ -3032,7 +3036,7 @@
       <c r="T3" s="5"/>
     </row>
     <row r="4" spans="1:20" ht="26.25" x14ac:dyDescent="0.25">
-      <c r="A4" s="37" t="s">
+      <c r="A4" s="27" t="s">
         <v>254</v>
       </c>
       <c r="B4" s="7" t="s">
@@ -3082,7 +3086,7 @@
       <c r="T4" s="5"/>
     </row>
     <row r="5" spans="1:20" ht="26.25" x14ac:dyDescent="0.25">
-      <c r="A5" s="37" t="s">
+      <c r="A5" s="27" t="s">
         <v>255</v>
       </c>
       <c r="B5" s="14" t="s">
@@ -3132,7 +3136,7 @@
       <c r="T5" s="5"/>
     </row>
     <row r="6" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A6" s="37" t="s">
+      <c r="A6" s="27" t="s">
         <v>326</v>
       </c>
       <c r="B6" s="7" t="s">
@@ -3180,7 +3184,7 @@
       <c r="T6" s="5"/>
     </row>
     <row r="7" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A7" s="37" t="s">
+      <c r="A7" s="27" t="s">
         <v>327</v>
       </c>
       <c r="B7" s="7" t="s">
@@ -3228,12 +3232,12 @@
       <c r="T7" s="5"/>
     </row>
     <row r="8" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A8" s="33" t="s">
+      <c r="A8" s="35" t="s">
         <v>259</v>
       </c>
-      <c r="B8" s="34"/>
-      <c r="C8" s="34"/>
-      <c r="D8" s="35"/>
+      <c r="B8" s="36"/>
+      <c r="C8" s="36"/>
+      <c r="D8" s="37"/>
       <c r="E8" s="9"/>
       <c r="F8" s="9"/>
       <c r="G8" s="9"/>
@@ -3590,12 +3594,12 @@
       <c r="T15" s="5"/>
     </row>
     <row r="16" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A16" s="36" t="s">
+      <c r="A16" s="38" t="s">
         <v>260</v>
       </c>
-      <c r="B16" s="36"/>
-      <c r="C16" s="36"/>
-      <c r="D16" s="36"/>
+      <c r="B16" s="38"/>
+      <c r="C16" s="38"/>
+      <c r="D16" s="38"/>
     </row>
     <row r="17" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A17" s="7" t="s">
@@ -4568,12 +4572,12 @@
       <c r="T36" s="5"/>
     </row>
     <row r="37" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A37" s="33" t="s">
+      <c r="A37" s="35" t="s">
         <v>262</v>
       </c>
-      <c r="B37" s="31"/>
-      <c r="C37" s="31"/>
-      <c r="D37" s="32"/>
+      <c r="B37" s="33"/>
+      <c r="C37" s="33"/>
+      <c r="D37" s="34"/>
       <c r="E37" s="9"/>
       <c r="F37" s="9"/>
       <c r="G37" s="9"/>
@@ -4942,12 +4946,12 @@
       <c r="T44" s="16"/>
     </row>
     <row r="45" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A45" s="30" t="s">
+      <c r="A45" s="32" t="s">
         <v>337</v>
       </c>
-      <c r="B45" s="31"/>
-      <c r="C45" s="31"/>
-      <c r="D45" s="32"/>
+      <c r="B45" s="33"/>
+      <c r="C45" s="33"/>
+      <c r="D45" s="34"/>
       <c r="E45" s="9"/>
       <c r="F45" s="9"/>
       <c r="G45" s="9"/>
@@ -4966,7 +4970,7 @@
       <c r="T45" s="6"/>
     </row>
     <row r="46" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A46" s="39" t="s">
+      <c r="A46" s="29" t="s">
         <v>325</v>
       </c>
       <c r="B46" s="7" t="s">
@@ -5020,7 +5024,7 @@
       <c r="T46" s="5"/>
     </row>
     <row r="47" spans="1:20" s="17" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A47" s="38" t="s">
+      <c r="A47" s="28" t="s">
         <v>328</v>
       </c>
       <c r="B47" s="15" t="s">
@@ -5074,7 +5078,7 @@
       <c r="T47" s="16"/>
     </row>
     <row r="48" spans="1:20" s="17" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A48" s="38" t="s">
+      <c r="A48" s="28" t="s">
         <v>329</v>
       </c>
       <c r="B48" s="15" t="s">
@@ -5122,7 +5126,7 @@
       <c r="T48" s="16"/>
     </row>
     <row r="49" spans="1:20" s="17" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A49" s="38" t="s">
+      <c r="A49" s="28" t="s">
         <v>330</v>
       </c>
       <c r="B49" s="15" t="s">
@@ -5174,7 +5178,7 @@
       <c r="T49" s="16"/>
     </row>
     <row r="50" spans="1:20" s="17" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A50" s="38" t="s">
+      <c r="A50" s="28" t="s">
         <v>331</v>
       </c>
       <c r="B50" s="15" t="s">
@@ -5226,7 +5230,7 @@
       <c r="T50" s="16"/>
     </row>
     <row r="51" spans="1:20" s="17" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A51" s="38" t="s">
+      <c r="A51" s="28" t="s">
         <v>332</v>
       </c>
       <c r="B51" s="15" t="s">
@@ -5278,7 +5282,7 @@
       <c r="T51" s="16"/>
     </row>
     <row r="52" spans="1:20" s="17" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A52" s="38" t="s">
+      <c r="A52" s="28" t="s">
         <v>333</v>
       </c>
       <c r="B52" s="15" t="s">
@@ -5330,7 +5334,7 @@
       <c r="T52" s="16"/>
     </row>
     <row r="53" spans="1:20" s="17" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A53" s="38" t="s">
+      <c r="A53" s="28" t="s">
         <v>334</v>
       </c>
       <c r="B53" s="15" t="s">
@@ -5382,7 +5386,7 @@
       <c r="T53" s="16"/>
     </row>
     <row r="54" spans="1:20" s="17" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A54" s="38" t="s">
+      <c r="A54" s="28" t="s">
         <v>335</v>
       </c>
       <c r="B54" s="15" t="s">
@@ -5436,7 +5440,7 @@
       <c r="T54" s="16"/>
     </row>
     <row r="55" spans="1:20" s="17" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A55" s="38" t="s">
+      <c r="A55" s="28" t="s">
         <v>336</v>
       </c>
       <c r="B55" s="15" t="s">
@@ -5490,12 +5494,12 @@
       <c r="T55" s="16"/>
     </row>
     <row r="56" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A56" s="30" t="s">
+      <c r="A56" s="32" t="s">
         <v>380</v>
       </c>
-      <c r="B56" s="31"/>
-      <c r="C56" s="31"/>
-      <c r="D56" s="32"/>
+      <c r="B56" s="33"/>
+      <c r="C56" s="33"/>
+      <c r="D56" s="34"/>
       <c r="E56" s="9"/>
       <c r="F56" s="9"/>
       <c r="G56" s="9"/>
@@ -5514,7 +5518,7 @@
       <c r="T56" s="6"/>
     </row>
     <row r="57" spans="1:20" s="17" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A57" s="15" t="s">
+      <c r="A57" s="28" t="s">
         <v>381</v>
       </c>
       <c r="B57" s="15" t="s">
@@ -5566,7 +5570,7 @@
       <c r="T57" s="16"/>
     </row>
     <row r="58" spans="1:20" s="17" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A58" s="15" t="s">
+      <c r="A58" s="28" t="s">
         <v>386</v>
       </c>
       <c r="B58" s="15" t="s">
@@ -5618,7 +5622,7 @@
       <c r="T58" s="16"/>
     </row>
     <row r="59" spans="1:20" s="17" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A59" s="15" t="s">
+      <c r="A59" s="28" t="s">
         <v>391</v>
       </c>
       <c r="B59" s="15" t="s">
@@ -5670,7 +5674,7 @@
       <c r="T59" s="16"/>
     </row>
     <row r="60" spans="1:20" s="17" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A60" s="15" t="s">
+      <c r="A60" s="28" t="s">
         <v>395</v>
       </c>
       <c r="B60" s="15" t="s">
@@ -5720,7 +5724,7 @@
       <c r="T60" s="16"/>
     </row>
     <row r="61" spans="1:20" s="17" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A61" s="15" t="s">
+      <c r="A61" s="28" t="s">
         <v>398</v>
       </c>
       <c r="B61" s="15" t="s">
@@ -5770,7 +5774,7 @@
       <c r="T61" s="16"/>
     </row>
     <row r="62" spans="1:20" s="17" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A62" s="15" t="s">
+      <c r="A62" s="28" t="s">
         <v>401</v>
       </c>
       <c r="B62" s="15" t="s">
@@ -5820,7 +5824,7 @@
       <c r="T62" s="16"/>
     </row>
     <row r="63" spans="1:20" s="17" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A63" s="15" t="s">
+      <c r="A63" s="28" t="s">
         <v>404</v>
       </c>
       <c r="B63" s="15" t="s">
@@ -5870,7 +5874,7 @@
       <c r="T63" s="16"/>
     </row>
     <row r="64" spans="1:20" s="17" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A64" s="15" t="s">
+      <c r="A64" s="28" t="s">
         <v>407</v>
       </c>
       <c r="B64" s="15" t="s">
@@ -5922,7 +5926,7 @@
       <c r="T64" s="16"/>
     </row>
     <row r="65" spans="1:20" s="17" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A65" s="15" t="s">
+      <c r="A65" s="28" t="s">
         <v>410</v>
       </c>
       <c r="B65" s="15" t="s">
@@ -5974,7 +5978,7 @@
       <c r="T65" s="16"/>
     </row>
     <row r="66" spans="1:20" s="17" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A66" s="15" t="s">
+      <c r="A66" s="28" t="s">
         <v>415</v>
       </c>
       <c r="B66" s="15" t="s">
@@ -6024,7 +6028,7 @@
       <c r="T66" s="16"/>
     </row>
     <row r="67" spans="1:20" s="17" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A67" s="15" t="s">
+      <c r="A67" s="28" t="s">
         <v>418</v>
       </c>
       <c r="B67" s="15" t="s">
@@ -6076,7 +6080,7 @@
       <c r="T67" s="16"/>
     </row>
     <row r="68" spans="1:20" s="17" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A68" s="15" t="s">
+      <c r="A68" s="28" t="s">
         <v>422</v>
       </c>
       <c r="B68" s="15" t="s">
@@ -6126,7 +6130,7 @@
       <c r="T68" s="16"/>
     </row>
     <row r="69" spans="1:20" s="17" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A69" s="15" t="s">
+      <c r="A69" s="28" t="s">
         <v>425</v>
       </c>
       <c r="B69" s="15" t="s">
@@ -6178,7 +6182,7 @@
       <c r="T69" s="16"/>
     </row>
     <row r="70" spans="1:20" s="17" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A70" s="38" t="s">
+      <c r="A70" s="28" t="s">
         <v>429</v>
       </c>
       <c r="B70" s="15" t="s">
@@ -6230,7 +6234,7 @@
       <c r="T70" s="16"/>
     </row>
     <row r="71" spans="1:20" s="17" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A71" s="15" t="s">
+      <c r="A71" s="28" t="s">
         <v>433</v>
       </c>
       <c r="B71" s="15" t="s">
@@ -6282,7 +6286,7 @@
       <c r="T71" s="16"/>
     </row>
     <row r="72" spans="1:20" s="17" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A72" s="15" t="s">
+      <c r="A72" s="28" t="s">
         <v>444</v>
       </c>
       <c r="B72" s="15" t="s">
@@ -6334,7 +6338,7 @@
       <c r="T72" s="16"/>
     </row>
     <row r="73" spans="1:20" s="17" customFormat="1" ht="39" x14ac:dyDescent="0.25">
-      <c r="A73" s="15" t="s">
+      <c r="A73" s="28" t="s">
         <v>448</v>
       </c>
       <c r="B73" s="15" t="s">
@@ -6386,7 +6390,7 @@
       <c r="T73" s="16"/>
     </row>
     <row r="74" spans="1:20" s="17" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A74" s="15" t="s">
+      <c r="A74" s="28" t="s">
         <v>453</v>
       </c>
       <c r="B74" s="15" t="s">
@@ -6438,7 +6442,7 @@
       <c r="T74" s="16"/>
     </row>
     <row r="75" spans="1:20" s="17" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A75" s="15" t="s">
+      <c r="A75" s="28" t="s">
         <v>456</v>
       </c>
       <c r="B75" s="15" t="s">
@@ -6490,7 +6494,7 @@
       <c r="T75" s="16"/>
     </row>
     <row r="76" spans="1:20" s="17" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A76" s="15" t="s">
+      <c r="A76" s="28" t="s">
         <v>460</v>
       </c>
       <c r="B76" s="15" t="s">
@@ -6540,7 +6544,7 @@
       <c r="T76" s="16"/>
     </row>
     <row r="77" spans="1:20" s="17" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A77" s="15" t="s">
+      <c r="A77" s="28" t="s">
         <v>465</v>
       </c>
       <c r="B77" s="15" t="s">
@@ -6590,7 +6594,7 @@
       <c r="T77" s="16"/>
     </row>
     <row r="78" spans="1:20" s="17" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A78" s="15" t="s">
+      <c r="A78" s="28" t="s">
         <v>468</v>
       </c>
       <c r="B78" s="15" t="s">
@@ -6642,7 +6646,7 @@
       <c r="T78" s="16"/>
     </row>
     <row r="79" spans="1:20" s="17" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A79" s="15" t="s">
+      <c r="A79" s="28" t="s">
         <v>472</v>
       </c>
       <c r="B79" s="15" t="s">
@@ -6694,7 +6698,7 @@
       <c r="T79" s="16"/>
     </row>
     <row r="80" spans="1:20" s="17" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A80" s="26" t="s">
+      <c r="A80" s="30" t="s">
         <v>476</v>
       </c>
       <c r="B80" s="26" t="s">
@@ -6744,7 +6748,7 @@
       <c r="T80" s="16"/>
     </row>
     <row r="81" spans="1:20" s="17" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A81" s="26" t="s">
+      <c r="A81" s="30" t="s">
         <v>479</v>
       </c>
       <c r="B81" s="26" t="s">
@@ -6794,7 +6798,7 @@
       <c r="T81" s="16"/>
     </row>
     <row r="82" spans="1:20" s="17" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A82" s="26" t="s">
+      <c r="A82" s="30" t="s">
         <v>482</v>
       </c>
       <c r="B82" s="26" t="s">
@@ -6846,7 +6850,7 @@
       <c r="T82" s="16"/>
     </row>
     <row r="83" spans="1:20" s="17" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A83" s="26" t="s">
+      <c r="A83" s="30" t="s">
         <v>486</v>
       </c>
       <c r="B83" s="26" t="s">
@@ -6898,7 +6902,7 @@
       <c r="T83" s="16"/>
     </row>
     <row r="84" spans="1:20" s="17" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A84" s="27" t="s">
+      <c r="A84" s="31" t="s">
         <v>491</v>
       </c>
       <c r="B84" s="26" t="s">
@@ -6950,7 +6954,7 @@
       <c r="T84" s="16"/>
     </row>
     <row r="85" spans="1:20" s="17" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A85" s="15" t="s">
+      <c r="A85" s="28" t="s">
         <v>496</v>
       </c>
       <c r="B85" s="15" t="s">
@@ -7000,7 +7004,7 @@
       <c r="T85" s="16"/>
     </row>
     <row r="86" spans="1:20" s="17" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A86" s="15" t="s">
+      <c r="A86" s="28" t="s">
         <v>500</v>
       </c>
       <c r="B86" s="15" t="s">
@@ -7052,7 +7056,7 @@
       <c r="T86" s="16"/>
     </row>
     <row r="87" spans="1:20" s="17" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A87" s="15" t="s">
+      <c r="A87" s="28" t="s">
         <v>504</v>
       </c>
       <c r="B87" s="15" t="s">
@@ -7102,7 +7106,7 @@
       <c r="T87" s="16"/>
     </row>
     <row r="88" spans="1:20" s="17" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A88" s="15" t="s">
+      <c r="A88" s="28" t="s">
         <v>507</v>
       </c>
       <c r="B88" s="15" t="s">
@@ -7152,7 +7156,7 @@
       <c r="T88" s="16"/>
     </row>
     <row r="89" spans="1:20" s="17" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A89" s="15" t="s">
+      <c r="A89" s="28" t="s">
         <v>511</v>
       </c>
       <c r="B89" s="15" t="s">
@@ -7202,12 +7206,12 @@
       <c r="T89" s="16"/>
     </row>
     <row r="90" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A90" s="30" t="s">
+      <c r="A90" s="32" t="s">
         <v>514</v>
       </c>
-      <c r="B90" s="31"/>
-      <c r="C90" s="31"/>
-      <c r="D90" s="32"/>
+      <c r="B90" s="33"/>
+      <c r="C90" s="33"/>
+      <c r="D90" s="34"/>
       <c r="E90" s="9"/>
       <c r="F90" s="9"/>
       <c r="G90" s="9"/>
@@ -7226,7 +7230,7 @@
       <c r="T90" s="6"/>
     </row>
     <row r="91" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A91" s="9" t="s">
+      <c r="A91" s="28" t="s">
         <v>525</v>
       </c>
       <c r="B91" s="9" t="s">
@@ -7276,7 +7280,7 @@
       </c>
     </row>
     <row r="92" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A92" s="9" t="s">
+      <c r="A92" s="28" t="s">
         <v>526</v>
       </c>
       <c r="B92" s="9" t="s">
@@ -7324,7 +7328,7 @@
       <c r="T92" s="6"/>
     </row>
     <row r="93" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A93" s="9" t="s">
+      <c r="A93" s="28" t="s">
         <v>527</v>
       </c>
       <c r="B93" s="9" t="s">
@@ -7374,7 +7378,7 @@
       </c>
     </row>
     <row r="94" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A94" s="9" t="s">
+      <c r="A94" s="28" t="s">
         <v>528</v>
       </c>
       <c r="B94" s="9" t="s">
@@ -7422,7 +7426,7 @@
       <c r="T94" s="6"/>
     </row>
     <row r="95" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A95" s="9" t="s">
+      <c r="A95" s="28" t="s">
         <v>529</v>
       </c>
       <c r="B95" s="9" t="s">
@@ -7470,7 +7474,7 @@
       <c r="T95" s="6"/>
     </row>
     <row r="96" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A96" s="9" t="s">
+      <c r="A96" s="30" t="s">
         <v>530</v>
       </c>
       <c r="B96" s="9" t="s">
@@ -7518,7 +7522,7 @@
       <c r="T96" s="6"/>
     </row>
     <row r="97" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A97" s="9" t="s">
+      <c r="A97" s="28" t="s">
         <v>533</v>
       </c>
       <c r="B97" s="9" t="s">
@@ -7568,7 +7572,7 @@
       <c r="T97" s="6"/>
     </row>
     <row r="98" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A98" s="9" t="s">
+      <c r="A98" s="30" t="s">
         <v>537</v>
       </c>
       <c r="B98" s="9" t="s">
@@ -7616,7 +7620,7 @@
       <c r="T98" s="6"/>
     </row>
     <row r="99" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A99" s="9" t="s">
+      <c r="A99" s="28" t="s">
         <v>540</v>
       </c>
       <c r="B99" s="9" t="s">
@@ -7668,7 +7672,7 @@
       </c>
     </row>
     <row r="100" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A100" s="9" t="s">
+      <c r="A100" s="30" t="s">
         <v>545</v>
       </c>
       <c r="B100" s="9" t="s">
@@ -7716,7 +7720,7 @@
       <c r="T100" s="6"/>
     </row>
     <row r="101" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A101" s="9" t="s">
+      <c r="A101" s="28" t="s">
         <v>549</v>
       </c>
       <c r="B101" s="9" t="s">
@@ -7766,7 +7770,7 @@
       <c r="T101" s="6"/>
     </row>
     <row r="102" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A102" s="9" t="s">
+      <c r="A102" s="30" t="s">
         <v>553</v>
       </c>
       <c r="B102" s="9" t="s">
@@ -7816,7 +7820,7 @@
       </c>
     </row>
     <row r="103" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A103" s="9" t="s">
+      <c r="A103" s="30" t="s">
         <v>557</v>
       </c>
       <c r="B103" s="9" t="s">
@@ -7864,7 +7868,7 @@
       <c r="T103" s="6"/>
     </row>
     <row r="104" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A104" s="9" t="s">
+      <c r="A104" s="28" t="s">
         <v>560</v>
       </c>
       <c r="B104" s="9" t="s">
@@ -7912,7 +7916,7 @@
       <c r="T104" s="6"/>
     </row>
     <row r="105" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A105" s="9" t="s">
+      <c r="A105" s="28" t="s">
         <v>562</v>
       </c>
       <c r="B105" s="9" t="s">
@@ -7962,7 +7966,7 @@
       <c r="T105" s="6"/>
     </row>
     <row r="106" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A106" s="9" t="s">
+      <c r="A106" s="28" t="s">
         <v>566</v>
       </c>
       <c r="B106" s="9" t="s">
@@ -8012,7 +8016,7 @@
       <c r="T106" s="6"/>
     </row>
     <row r="107" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A107" s="9" t="s">
+      <c r="A107" s="28" t="s">
         <v>571</v>
       </c>
       <c r="B107" s="9" t="s">
@@ -8060,7 +8064,7 @@
       <c r="T107" s="6"/>
     </row>
     <row r="108" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A108" s="9" t="s">
+      <c r="A108" s="28" t="s">
         <v>574</v>
       </c>
       <c r="B108" s="9" t="s">
@@ -8108,7 +8112,7 @@
       <c r="T108" s="6"/>
     </row>
     <row r="109" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A109" s="9" t="s">
+      <c r="A109" s="28" t="s">
         <v>577</v>
       </c>
       <c r="B109" s="9" t="s">
@@ -8158,7 +8162,7 @@
       </c>
     </row>
     <row r="110" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A110" s="9" t="s">
+      <c r="A110" s="28" t="s">
         <v>581</v>
       </c>
       <c r="B110" s="9" t="s">
@@ -8206,7 +8210,7 @@
       </c>
     </row>
     <row r="111" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A111" s="9" t="s">
+      <c r="A111" s="28" t="s">
         <v>585</v>
       </c>
       <c r="B111" s="9" t="s">
@@ -8256,7 +8260,7 @@
       <c r="T111" s="6"/>
     </row>
     <row r="112" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A112" s="9" t="s">
+      <c r="A112" s="28" t="s">
         <v>589</v>
       </c>
       <c r="B112" s="9" t="s">
@@ -8306,7 +8310,7 @@
       <c r="T112" s="6"/>
     </row>
     <row r="113" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A113" s="9" t="s">
+      <c r="A113" s="28" t="s">
         <v>593</v>
       </c>
       <c r="B113" s="9" t="s">
@@ -8356,7 +8360,7 @@
       <c r="T113" s="6"/>
     </row>
     <row r="114" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A114" s="9" t="s">
+      <c r="A114" s="28" t="s">
         <v>597</v>
       </c>
       <c r="B114" s="9" t="s">
@@ -8404,7 +8408,7 @@
       <c r="T114" s="6"/>
     </row>
     <row r="115" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A115" s="9" t="s">
+      <c r="A115" s="28" t="s">
         <v>600</v>
       </c>
       <c r="B115" s="9" t="s">
@@ -8454,7 +8458,7 @@
       <c r="T115" s="6"/>
     </row>
     <row r="116" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A116" s="9" t="s">
+      <c r="A116" s="28" t="s">
         <v>604</v>
       </c>
       <c r="B116" s="9" t="s">
@@ -8502,7 +8506,7 @@
       <c r="T116" s="6"/>
     </row>
     <row r="117" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A117" s="9" t="s">
+      <c r="A117" s="28" t="s">
         <v>607</v>
       </c>
       <c r="B117" s="9" t="s">
@@ -8550,7 +8554,7 @@
       <c r="T117" s="6"/>
     </row>
     <row r="118" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A118" s="9" t="s">
+      <c r="A118" s="28" t="s">
         <v>608</v>
       </c>
       <c r="B118" s="9" t="s">
@@ -8598,7 +8602,7 @@
       <c r="T118" s="6"/>
     </row>
     <row r="119" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A119" s="9" t="s">
+      <c r="A119" s="28" t="s">
         <v>612</v>
       </c>
       <c r="B119" s="9" t="s">
@@ -8648,7 +8652,7 @@
       </c>
     </row>
     <row r="120" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A120" s="9" t="s">
+      <c r="A120" s="28" t="s">
         <v>616</v>
       </c>
       <c r="B120" s="9" t="s">
@@ -8698,7 +8702,7 @@
       <c r="T120" s="6"/>
     </row>
     <row r="121" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A121" s="9" t="s">
+      <c r="A121" s="28" t="s">
         <v>620</v>
       </c>
       <c r="B121" s="9" t="s">
@@ -8748,7 +8752,7 @@
       <c r="T121" s="6"/>
     </row>
     <row r="122" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A122" s="9" t="s">
+      <c r="A122" s="28" t="s">
         <v>623</v>
       </c>
       <c r="B122" s="9" t="s">
@@ -8798,7 +8802,7 @@
       <c r="T122" s="6"/>
     </row>
     <row r="123" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A123" s="9" t="s">
+      <c r="A123" s="28" t="s">
         <v>627</v>
       </c>
       <c r="B123" s="9" t="s">
@@ -8846,7 +8850,7 @@
       <c r="T123" s="6"/>
     </row>
     <row r="124" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A124" s="9" t="s">
+      <c r="A124" s="28" t="s">
         <v>629</v>
       </c>
       <c r="B124" s="9" t="s">
@@ -8896,7 +8900,7 @@
       <c r="T124" s="6"/>
     </row>
     <row r="125" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A125" s="9" t="s">
+      <c r="A125" s="28" t="s">
         <v>633</v>
       </c>
       <c r="B125" s="9" t="s">
@@ -8944,7 +8948,7 @@
       <c r="T125" s="6"/>
     </row>
     <row r="126" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A126" s="9" t="s">
+      <c r="A126" s="28" t="s">
         <v>636</v>
       </c>
       <c r="B126" s="9" t="s">
@@ -8994,7 +8998,7 @@
       <c r="T126" s="6"/>
     </row>
     <row r="127" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A127" s="9" t="s">
+      <c r="A127" s="28" t="s">
         <v>640</v>
       </c>
       <c r="B127" s="9" t="s">
@@ -9044,7 +9048,7 @@
       <c r="T127" s="6"/>
     </row>
     <row r="128" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A128" s="9" t="s">
+      <c r="A128" s="28" t="s">
         <v>644</v>
       </c>
       <c r="B128" s="9" t="s">
@@ -9094,7 +9098,7 @@
       <c r="T128" s="6"/>
     </row>
     <row r="129" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A129" s="9" t="s">
+      <c r="A129" s="28" t="s">
         <v>648</v>
       </c>
       <c r="B129" s="9" t="s">
@@ -9146,7 +9150,7 @@
       <c r="T129" s="6"/>
     </row>
     <row r="130" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A130" s="9" t="s">
+      <c r="A130" s="28" t="s">
         <v>652</v>
       </c>
       <c r="B130" s="9" t="s">
@@ -9196,7 +9200,7 @@
       <c r="T130" s="6"/>
     </row>
     <row r="131" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A131" s="9" t="s">
+      <c r="A131" s="28" t="s">
         <v>656</v>
       </c>
       <c r="B131" s="9" t="s">
@@ -9246,7 +9250,7 @@
       </c>
     </row>
     <row r="132" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A132" s="9" t="s">
+      <c r="A132" s="28" t="s">
         <v>660</v>
       </c>
       <c r="B132" s="9" t="s">
@@ -9296,7 +9300,7 @@
       <c r="T132" s="6"/>
     </row>
     <row r="133" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A133" s="9" t="s">
+      <c r="A133" s="28" t="s">
         <v>664</v>
       </c>
       <c r="B133" s="9" t="s">
@@ -9344,7 +9348,7 @@
       <c r="T133" s="6"/>
     </row>
     <row r="134" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A134" s="38" t="s">
+      <c r="A134" s="28" t="s">
         <v>667</v>
       </c>
       <c r="B134" s="9" t="s">
@@ -9394,7 +9398,7 @@
       </c>
     </row>
     <row r="135" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A135" s="9" t="s">
+      <c r="A135" s="28" t="s">
         <v>671</v>
       </c>
       <c r="B135" s="9" t="s">
@@ -9442,7 +9446,7 @@
       <c r="T135" s="6"/>
     </row>
     <row r="136" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A136" s="9" t="s">
+      <c r="A136" s="28" t="s">
         <v>674</v>
       </c>
       <c r="B136" s="9" t="s">
@@ -9492,7 +9496,7 @@
       <c r="T136" s="6"/>
     </row>
     <row r="137" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A137" s="9" t="s">
+      <c r="A137" s="28" t="s">
         <v>678</v>
       </c>
       <c r="B137" s="9" t="s">
@@ -9540,7 +9544,7 @@
       <c r="T137" s="6"/>
     </row>
     <row r="138" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A138" s="9" t="s">
+      <c r="A138" s="28" t="s">
         <v>681</v>
       </c>
       <c r="B138" s="9" t="s">
@@ -9590,7 +9594,7 @@
       <c r="T138" s="6"/>
     </row>
     <row r="139" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A139" s="9" t="s">
+      <c r="A139" s="28" t="s">
         <v>685</v>
       </c>
       <c r="B139" s="9" t="s">
@@ -9638,7 +9642,7 @@
       <c r="T139" s="6"/>
     </row>
     <row r="140" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A140" s="9" t="s">
+      <c r="A140" s="28" t="s">
         <v>688</v>
       </c>
       <c r="B140" s="9" t="s">
@@ -9686,7 +9690,7 @@
       <c r="T140" s="6"/>
     </row>
     <row r="141" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A141" s="9" t="s">
+      <c r="A141" s="28" t="s">
         <v>691</v>
       </c>
       <c r="B141" s="9" t="s">
@@ -9736,7 +9740,7 @@
       <c r="T141" s="6"/>
     </row>
     <row r="142" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A142" s="9" t="s">
+      <c r="A142" s="28" t="s">
         <v>695</v>
       </c>
       <c r="B142" s="9" t="s">
@@ -9786,7 +9790,7 @@
       <c r="T142" s="6"/>
     </row>
     <row r="143" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A143" s="9" t="s">
+      <c r="A143" s="28" t="s">
         <v>698</v>
       </c>
       <c r="B143" s="9" t="s">
@@ -13065,7 +13069,7 @@
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A2" s="5" t="s">
+      <c r="A2" s="41" t="s">
         <v>152</v>
       </c>
       <c r="B2" s="5" t="s">
@@ -13088,7 +13092,7 @@
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A3" s="5" t="s">
+      <c r="A3" s="41" t="s">
         <v>153</v>
       </c>
       <c r="B3" s="5" t="s">
@@ -13109,7 +13113,7 @@
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A4" s="5" t="s">
+      <c r="A4" s="41" t="s">
         <v>154</v>
       </c>
       <c r="B4" s="5" t="s">
@@ -13130,7 +13134,7 @@
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A5" s="5" t="s">
+      <c r="A5" s="41" t="s">
         <v>155</v>
       </c>
       <c r="B5" s="5" t="s">
@@ -13151,7 +13155,7 @@
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A6" s="5" t="s">
+      <c r="A6" s="41" t="s">
         <v>156</v>
       </c>
       <c r="B6" s="5" t="s">
@@ -14572,92 +14576,92 @@
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A1" s="28" t="s">
+      <c r="A1" s="39" t="s">
         <v>702</v>
       </c>
-      <c r="B1" s="28"/>
-      <c r="C1" s="28"/>
-      <c r="D1" s="28"/>
-      <c r="E1" s="28"/>
-      <c r="F1" s="28"/>
+      <c r="B1" s="39"/>
+      <c r="C1" s="39"/>
+      <c r="D1" s="39"/>
+      <c r="E1" s="39"/>
+      <c r="F1" s="39"/>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A2" s="29" t="s">
+      <c r="A2" s="40" t="s">
         <v>703</v>
       </c>
-      <c r="B2" s="29"/>
-      <c r="C2" s="29"/>
-      <c r="D2" s="29"/>
-      <c r="E2" s="29"/>
-      <c r="F2" s="29"/>
+      <c r="B2" s="40"/>
+      <c r="C2" s="40"/>
+      <c r="D2" s="40"/>
+      <c r="E2" s="40"/>
+      <c r="F2" s="40"/>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A3" s="29"/>
-      <c r="B3" s="29"/>
-      <c r="C3" s="29"/>
-      <c r="D3" s="29"/>
-      <c r="E3" s="29"/>
-      <c r="F3" s="29"/>
+      <c r="A3" s="40"/>
+      <c r="B3" s="40"/>
+      <c r="C3" s="40"/>
+      <c r="D3" s="40"/>
+      <c r="E3" s="40"/>
+      <c r="F3" s="40"/>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A4" s="28" t="s">
+      <c r="A4" s="39" t="s">
         <v>704</v>
       </c>
-      <c r="B4" s="28"/>
+      <c r="B4" s="39"/>
       <c r="C4" t="s">
         <v>705</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A5" s="28" t="s">
+      <c r="A5" s="39" t="s">
         <v>706</v>
       </c>
-      <c r="B5" s="28"/>
+      <c r="B5" s="39"/>
       <c r="C5" t="s">
         <v>707</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A6" s="28" t="s">
+      <c r="A6" s="39" t="s">
         <v>708</v>
       </c>
-      <c r="B6" s="28"/>
+      <c r="B6" s="39"/>
       <c r="C6" t="s">
         <v>709</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A7" s="28" t="s">
+      <c r="A7" s="39" t="s">
         <v>710</v>
       </c>
-      <c r="B7" s="28"/>
+      <c r="B7" s="39"/>
       <c r="C7" t="s">
         <v>711</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A8" s="28" t="s">
+      <c r="A8" s="39" t="s">
         <v>712</v>
       </c>
-      <c r="B8" s="28"/>
+      <c r="B8" s="39"/>
       <c r="C8" t="s">
         <v>713</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A9" s="28" t="s">
+      <c r="A9" s="39" t="s">
         <v>714</v>
       </c>
-      <c r="B9" s="28"/>
+      <c r="B9" s="39"/>
       <c r="C9" t="s">
         <v>715</v>
       </c>
     </row>
     <row r="10" spans="1:6" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="29" t="s">
+      <c r="A10" s="40" t="s">
         <v>716</v>
       </c>
-      <c r="B10" s="29"/>
+      <c r="B10" s="40"/>
       <c r="C10" t="s">
         <v>717</v>
       </c>
